--- a/experiments/rq1-3-4-5/methods/visidroid/all_tasks.xlsx
+++ b/experiments/rq1-3-4-5/methods/visidroid/all_tasks.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minhh\OneDrive\Documents\mobile-testing\methods\visidroid\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FD0CF6-DBE5-4AA7-AD93-6DBDF8AA7DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$152</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -56,6 +34,15 @@
     <t>soa</t>
   </si>
   <si>
+    <t>VALID</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
     <t>applauncher</t>
   </si>
   <si>
@@ -161,6 +148,9 @@
     <t>Close the shutter sound</t>
   </si>
   <si>
+    <t>Compress the photos by 50%</t>
+  </si>
+  <si>
     <t>Delete the last photo I took</t>
   </si>
   <si>
@@ -176,6 +166,21 @@
     <t>Rotate right the last picture I took and save it as pic4.jpg</t>
   </si>
   <si>
+    <t>Take a photo and add it to favorite</t>
+  </si>
+  <si>
+    <t>Take a photo and move it to folder 'movies' in SD card</t>
+  </si>
+  <si>
+    <t>Take a photo and name it 'sunset'</t>
+  </si>
+  <si>
+    <t>Take a photo and report its size</t>
+  </si>
+  <si>
+    <t>Take a photo and resize it to 1000:473</t>
+  </si>
+  <si>
     <t>Take a selfie</t>
   </si>
   <si>
@@ -185,24 +190,6 @@
     <t>Use volume button as shutter</t>
   </si>
   <si>
-    <t>add the last photo to favorite</t>
-  </si>
-  <si>
-    <t>check the size of the last photo i took</t>
-  </si>
-  <si>
-    <t>move the last photo i took to folder 'movies' in sd card</t>
-  </si>
-  <si>
-    <t>rename the last photo to 'sunset'</t>
-  </si>
-  <si>
-    <t>resize the last photo to 1000:473</t>
-  </si>
-  <si>
-    <t>set photo compression quality to 50%</t>
-  </si>
-  <si>
     <t>Add a new timer of 5:00</t>
   </si>
   <si>
@@ -293,36 +280,36 @@
     <t>Create a new contact Alice, mobile number 31232134</t>
   </si>
   <si>
+    <t>Create a new contact John Smith, mobile number 12345678900</t>
+  </si>
+  <si>
     <t>Delete all call history</t>
   </si>
   <si>
     <t>Delete contact Jack</t>
   </si>
   <si>
+    <t>Find a Contact Alice</t>
+  </si>
+  <si>
+    <t>Modify Alice's mobile number to 1234567890</t>
+  </si>
+  <si>
+    <t>Sort contacts by first name in ascending order</t>
+  </si>
+  <si>
+    <t>Switch custom colors to light</t>
+  </si>
+  <si>
+    <t>Text Alice that I love you</t>
+  </si>
+  <si>
     <t>Turn on hide dialpad numbers</t>
   </si>
   <si>
     <t>View Favorite Contacts</t>
   </si>
   <si>
-    <t>create a new contact john smith, moblie number 12345678900</t>
-  </si>
-  <si>
-    <t>modify alice's mobile number to 1234567890 and save it</t>
-  </si>
-  <si>
-    <t>search contact alice and check her info</t>
-  </si>
-  <si>
-    <t>sort contacts by first name</t>
-  </si>
-  <si>
-    <t>switch custom colors to light and save it</t>
-  </si>
-  <si>
-    <t>text alice that i-love-you</t>
-  </si>
-  <si>
     <t>Add 'alarms' as favorite</t>
   </si>
   <si>
@@ -476,6 +463,9 @@
     <t>Create a checklist note called 'NewCheckList'</t>
   </si>
   <si>
+    <t>Create a new text note called 'test' and type '123456'</t>
+  </si>
+  <si>
     <t>Create a text note called 'test', type '12345678', and search for '234'</t>
   </si>
   <si>
@@ -494,9 +484,6 @@
     <t>Rename the note 'diary' to 'events'</t>
   </si>
   <si>
-    <t>create a new note called 'test' and type '123456'</t>
-  </si>
-  <si>
     <t>disable autosave notes</t>
   </si>
   <si>
@@ -605,6 +592,9 @@
     <t>Jade Green successfully disabled the shutter sound in the Camera app by navigating to the Settings page and unchecking the "Shutter sound" checkbox.</t>
   </si>
   <si>
+    <t>Jade Green successfully changed the photo compression quality to 50% in the Camera app.</t>
+  </si>
+  <si>
     <t>Jade Green successfully deleted the last photo taken using the Camera app.</t>
   </si>
   <si>
@@ -620,6 +610,21 @@
     <t>Jade Green successfully rotated the last picture taken to the right but did not save it as "pic4.jpg".</t>
   </si>
   <si>
+    <t>Jade Green attempted success take a photo and add to favorite.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to take a photo and move it to the 'movies' folder on the SD card but failed to complete the task as no actions related to moving the photo were performed.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to take a photo and name it 'sunset' but ended up discontinuing the task due to complications in managing the app's interface, specifically in renaming the photo.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully took a photo and accessed its details to report the size.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to take a photo and resize it, but got sidetracked with adjusting photo compression settings repeatedly without resizing the photo.</t>
+  </si>
+  <si>
     <t>Jade Green successfully took a selfie using the Camera app.</t>
   </si>
   <si>
@@ -629,24 +634,6 @@
     <t>Jade Green successfully enabled the use of volume buttons as a shutter on the Camera app.</t>
   </si>
   <si>
-    <t>Jade Green attempted success take a photo and add to favorite.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully took a photo and accessed its details to report the size.</t>
-  </si>
-  <si>
-    <t>Jade Green attempted to take a photo and move it to the 'movies' folder on the SD card but failed to complete the task as no actions related to moving the photo were performed.</t>
-  </si>
-  <si>
-    <t>Jade Green attempted to take a photo and name it 'sunset' but ended up discontinuing the task due to complications in managing the app's interface, specifically in renaming the photo.</t>
-  </si>
-  <si>
-    <t>Jade Green attempted to take a photo and resize it, but got sidetracked with adjusting photo compression settings repeatedly without resizing the photo.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully changed the photo compression quality to 50% in the Camera app.</t>
-  </si>
-  <si>
     <t>Jade Green successfully added a new timer set for 5:00 on the Clock app.</t>
   </si>
   <si>
@@ -740,36 +727,36 @@
     <t>Jade Green successfully created a new contact named Alice with the mobile number 31232134 in the Dialer app.</t>
   </si>
   <si>
+    <t>Jade Green successfully created a new contact named John Smith with the mobile number 12345678900 in the Dialer app.</t>
+  </si>
+  <si>
     <t>Jade Green attempted to delete all call history but did not successfully complete the task, as evidenced by repeated attempts to access the call history without further action.</t>
   </si>
   <si>
     <t>Jade Green successfully deleted the contact named Jack from the Dialer app.</t>
   </si>
   <si>
+    <t>Jade Green successfully located and accessed the contact details for Alice on the Dialer app.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully updated Alice's mobile number to 1234567890 in the Dialer app.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully sorted the contacts by first name in ascending order, as evidenced by the ordered list of contacts displayed on the Main page.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully switched the custom colors from dark to light in the Dialer app.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully sent a text message saying "I love you" to Alice.</t>
+  </si>
+  <si>
     <t>Jade Green successfully enabled the option to hide dialpad numbers in the Dialer app.</t>
   </si>
   <si>
     <t>Jade Green view favorite contacts by pressing the "Favorites" button</t>
   </si>
   <si>
-    <t>Jade Green successfully created a new contact named John Smith with the mobile number 12345678900 in the Dialer app.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully updated Alice's mobile number to 1234567890 in the Dialer app.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully located and accessed the contact details for Alice on the Dialer app.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully sorted the contacts by first name in ascending order, as evidenced by the ordered list of contacts displayed on the Main page.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully switched the custom colors from dark to light in the Dialer app.</t>
-  </si>
-  <si>
-    <t>Jade Green successfully sent a text message saying "I love you" to Alice.</t>
-  </si>
-  <si>
     <t>Jade Green successfully added the 'alarms' folder to favorites, as indicated by the option to remove it from favorites now being available.</t>
   </si>
   <si>
@@ -929,6 +916,9 @@
     <t>Jade Green successfully created a checklist note titled "NewCheckList" in the Notes app.</t>
   </si>
   <si>
+    <t>Jade Green successfully created a new text note named 'test' and typed '123456' in it.</t>
+  </si>
+  <si>
     <t>Jade Green fail to created a text note titled 'test', typed '12345678' into it, and performed a search for '234'.</t>
   </si>
   <si>
@@ -945,9 +935,6 @@
   </si>
   <si>
     <t>Jade Green successfully renamed the note from "diary" to "events".</t>
-  </si>
-  <si>
-    <t>Jade Green successfully created a new text note named 'test' and typed '123456' in it.</t>
   </si>
   <si>
     <t>Jade Green successfully navigated to the Settings page and disabled the "Autosave notes" feature.</t>
@@ -1024,32 +1011,23 @@
 - ACTION 3: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "New Event"
-- ACTION 2: touched on a button that has text "Event"
-- ACTION 3: filled a focused textfield that has text "Title" with the text "John Doe's Birthday"
-- ACTION 4: touched on a button that has text "September 10 (Tue)"
-- ACTION 5: touched on a button that has text "OK"
-- ACTION 6: touched on a button that has content-desc "Save"
-- ACTION 7: touched on a button that has content-desc "New Event"
-- ACTION 8: touched on a button that has text "Event"
-- ACTION 9: filled a focused textfield that has text "Title" with the text "Jane Smith's Birthday"
-- ACTION 10: touched on a button that has text "September 10 (Tue)"
-- ACTION 11: touched on a button that has text "OK"
-- ACTION 12: touched on a button that has content-desc "Save"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "New Event"
-- ACTION 2: touched on a button that has content-desc "New Event"
-- ACTION 3: filled a focused textfield that has text "Title" with the text "John's Anniversary"
-- ACTION 4: touched on a button that has text "September 10 (Tue)"
-- ACTION 5: touched on a button that has text "OK"
-- ACTION 6: touched on a button that has content-desc "Save"
-- ACTION 7: touched on a button that has content-desc "New Event"
-- ACTION 8: touched on a button that has text "Event"
-- ACTION 9: filled a focused textfield that has text "Title" with the text "Sarah's Anniversary"
-- ACTION 10: touched on a button that has text "September 10 (Tue)"
-- ACTION 11: touched on a button that has text "OK"
-- ACTION 12: touched on a button that has content-desc "Save"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Add contact birthdays"
+- ACTION 3: Jade Green touched on a button that has text "OK"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Anniversaries"
+- ACTION 2: Jade Green touched on a button that has content_desc "New Event"
+- ACTION 3: Jade Green touched on a button that has text "Event"
+- ACTION 4: Jade Green filled a focused textfield that has text "Title" with the text "John Doe Anniversary"
+- ACTION 5: Jade Green touched on a button that has text "No repetition"
+- ACTION 6: Jade Green touched on a button that has text "Yearly"
+- ACTION 7: Jade Green touched on a button that has text "February 13 (Thu)"
+- ACTION 8: Jade Green touched on a button that has text "OK"
+- ACTION 9: Jade Green touched on a checkbox that has text "All-day"
+- ACTION 10: Jade Green touched on a button that has content_desc "Save"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "New Event"
@@ -1092,19 +1070,14 @@
 - ACTION 13: scrolled down on a scrollable area that has text "Algeria, Argentina, Australia[...and more]"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
-- ACTION 3: touched on a button that has text "CalDAV sync"
-- ACTION 4: touched on a button that has text "ALLOW"
-- ACTION 5: touched on a button that has text "Cancel"
-- ACTION 6: scrolled down on a scrollable area that has text "Always use same snooze time, Snooze time, 30 minutes[...and more]"
-- ACTION 7: touched on a button that has content-desc "Back"
-- ACTION 8: touched on a button that has content-desc "More options"
-- ACTION 9: touched on a button that has text "Add holidays"
-- ACTION 10: scrolled down on a scrollable area that has text "Algeria, Argentina, Australia[...and more]"
-- ACTION 11: scrolled down on a scrollable area that has text "Hellas, Hrvatska, India[...and more]"
-- ACTION 12: scrolled down on a scrollable area that has text "æ—¥æœ¬, Nigeria, Norge[...and more]"
-- ACTION 13: touched on a button that has text "United States"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Add holidays"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "Algeria, Argentina, Australia[...and more]"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "Hellas, Hrvatska, India[...and more]"
+- ACTION 5: Jade Green scrolled down on a scrollable area that has text "Nigeria, Norge, Österreich[...and more]"
+- ACTION 6: Jade Green touched on a button that has text "United States"
+- ACTION 7: Jade Green touched on a button that has text "OK"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1138,19 +1111,12 @@
 - ACTION 4: touched on a button that has content-desc "Save"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: pressed "BACK" button to navigate back
-- ACTION 3: touched on a button that has content-desc "Change view"
-- ACTION 4: pressed "BACK" button to navigate back
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: pressed "BACK" button to navigate back
-- ACTION 7: touched on a button that has content-desc "Search"
-- ACTION 8: pressed "BACK" button to navigate back
-- ACTION 9: touched on a button that has content-desc "More options"
-- ACTION 10: pressed "BACK" button to navigate back
-- ACTION 11: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/small_month_view"
-- ACTION 12: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- ACTION 13: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/top_right_arrow"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "New Event"
+- ACTION 2: Jade Green filled a focused textfield that has text "Title" with the text "homework"
+- ACTION 3: Jade Green touched on a button that has text "No repetition"
+- ACTION 4: Jade Green touched on a button that has text "Daily"
+- ACTION 5: Jade Green touched on a button that has content_desc "Save"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -1170,19 +1136,17 @@
 - ACTION 3: touched on a button that has text "Monday"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: pressed "BACK" button to navigate back
-- ACTION 3: touched on a button that has content-desc "Settings"
-- ACTION 4: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
-- ACTION 5: scrolled down on a scrollable area that has text "Always use same snooze time, Snooze time, 30 minutes[...and more]"
-- ACTION 6: scrolled down on a scrollable area that has text "Allow customizing day count, Start week with the current day, MONTHLY VIEW[...and more]"
-- ACTION 7: touched on a button that has text "Export events to an .ics file"
-- ACTION 8: filled a textfield that has text "Events_2024_09_10_19_07_52" with the text "DCIM/test.ics"
-- ACTION 9: touched on a button that has text "OK"
-- ACTION 10: filled a focused textfield that has text "DCIM/test.ics" with the text "test.ics"
-- ACTION 11: touched on a button that has text "OK"
-- ACTION 12: filled a textfield that has text "test.ics.ics" with the text "test.ics"
-- ACTION 13: touched on a button that has text "SAVE"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has content_desc "Back"
+- ACTION 4: Jade Green touched on a button that has content_desc "More options"
+- ACTION 5: Jade Green touched on a button that has text "Print"
+- ACTION 6: Jade Green touched on a button that has content_desc "Save to PDF"
+- ACTION 7: Jade Green pressed "BACK" button to navigate back
+- ACTION 8: Jade Green touched on a button that has content_desc "More options"
+- ACTION 9: Jade Green pressed "BACK" button to navigate back
+- ACTION 10: Jade Green touched on a button that has content_desc "More options"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Search"
@@ -1196,6 +1160,11 @@
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
 - ACTION 2: touched on a checked checkbox that has text "Shutter sound"
 - ACTION 3: touched on a checkbox that has text "Shutter sound"</t>
+  </si>
+  <si>
+    <t>- ACTION 1: touched on a button that has content-desc "Settings"
+- ACTION 2: touched on a button that has text "Photo compression quality, 80%"
+- ACTION 3: touched on a button that has text "50%"</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "View last captured media"
@@ -1207,21 +1176,11 @@
     <t>- ACTION 1: touched on a button that has content-desc "View last captured media"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "View last captured media"
-- ACTION 2: touched on a button that has content-desc "More options"
-- ACTION 3: touched on a button that has text "Set picture as"
-- ACTION 4: touched on a button that has text "Gallery, Wallpaper"
-- ACTION 5: pressed "BACK" button to navigate back
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: Press the back button 2 times because you stayed on the pages not belonging to the target app for too long
-- ACTION 8: touched on a button that has content-desc "View last captured media"
-- ACTION 9: touched on a button that has content-desc "More options"
-- ACTION 10: touched on a button that has text "Set picture as"
-- ACTION 11: touched on a button that has text "Gallery, Wallpaper"
-- ACTION 12: pressed "BACK" button to navigate back
-- ACTION 13: touched on a button that has content-desc "More options"
-- ACTION 14: Press the back button 2 times because you stayed on the pages not belonging to the target app for too long
-- ACTION 15: touched on a button that has content-desc "View last captured media"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green pressed "BACK" button to navigate back
+- ACTION 2: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 3: Jade Green touched on a button that has text "Just once"
+- ACTION 4: Jade Green touched on a button that has content_desc "Share with Print"
+</t>
   </si>
   <si>
     <t>- ACTION 1: pressed "BACK" button to navigate back
@@ -1231,39 +1190,19 @@
 - ACTION 5: touched on a button that has content-desc "Shutter"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "View last captured media"
-- ACTION 2: touched on a button that has content-desc "More options"
-- ACTION 3: touched on a button that has text "Rotate right"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: pressed "BACK" button to navigate back</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Toggle front/back camera"
-- ACTION 2: touched on a button that has content-desc "Shutter"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Camera"
-- ACTION 2: touched on a button that has content-desc "Toggle front/back camera"
-- ACTION 3: touched on a button that has text "Video"
-- ACTION 4: touched on a button that has content-desc "Shutter"
-- ACTION 5: touched on a selected button that has content-desc "Shutter"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a checkbox that has text "Use volume buttons as shutter"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 2: Jade Green touched on a button that has text "Just once"
+- ACTION 3: Jade Green touched on a button that has content_desc "More options"
+- ACTION 4: Jade Green touched on a button that has content_desc "DCIM, Navigate up"
+- ACTION 5: Jade Green touched on a button that has content_desc "More options"
+- ACTION 6: Press the back button because you stayed on the pages not belonging to the target app for too long
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Photo"
 - ACTION 2: touched on a button that has content-desc "Shutter"
 - ACTION 3: touched on a button that has content-desc "View last captured media"
 - ACTION 4: touched on a button that has content-desc "Favorite"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Shutter"
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: touched on a button that has text "Details"</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Shutter"
@@ -1294,6 +1233,12 @@
 - ACTION 14: touched on a button that has text "Close"</t>
   </si>
   <si>
+    <t>- ACTION 1: touched on a button that has content-desc "Shutter"
+- ACTION 2: touched on a button that has content-desc "View last captured media"
+- ACTION 3: touched on a button that has content-desc "More options"
+- ACTION 4: touched on a button that has text "Details"</t>
+  </si>
+  <si>
     <t>- ACTION 1: touched on a button that has text "Photo"
 - ACTION 2: touched on a button that has content-desc "Shutter"
 - ACTION 3: touched on a button that has content-desc "Settings"
@@ -1309,9 +1254,19 @@
 - ACTION 13: touched on a button that has text "Photo compression quality, 50%"</t>
   </si>
   <si>
+    <t>- ACTION 1: touched on a button that has content-desc "Toggle front/back camera"
+- ACTION 2: touched on a button that has content-desc "Shutter"</t>
+  </si>
+  <si>
+    <t>- ACTION 1: touched on a button that has text "Camera"
+- ACTION 2: touched on a button that has content-desc "Toggle front/back camera"
+- ACTION 3: touched on a button that has text "Video"
+- ACTION 4: touched on a button that has content-desc "Shutter"
+- ACTION 5: touched on a selected button that has content-desc "Shutter"</t>
+  </si>
+  <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a button that has text "Photo compression quality, 80%"
-- ACTION 3: touched on a button that has text "50%"</t>
+- ACTION 2: touched on a checkbox that has text "Use volume buttons as shutter"</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Timer"
@@ -1350,19 +1305,8 @@
 - ACTION 3: touched on a button that has text "5 minutes"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
-- ACTION 3: touched on a button that has text "Max reminder duration, 5 minutes"
-- ACTION 4: pressed "BACK" button to navigate back
-- ACTION 5: scrolled down on a scrollable area that has text "Customize widget colors, GENERAL, Prevent phone from sleeping while the app is in fo[...][...and more]"
-- ACTION 6: touched on a button that has text "Snooze time, 5 minutes"
-- ACTION 7: pressed "BACK" button to navigate back
-- ACTION 8: scrolled down on a scrollable area that has text "Customize widget colors, GENERAL, Prevent phone from sleeping while the app is in fo[...][...and more]"
-- ACTION 9: touched on a button that has text "Always use same snooze time"
-- ACTION 10: scrolled down on a scrollable area that has text "Customize colors, Customize widget colors, GENERAL[...and more]"
-- ACTION 11: scrolled down on a scrollable area that has text "Customize colors, Customize widget colors, GENERAL[...and more]"
-- ACTION 12: touched on a button that has text "Max reminder duration, 5 minutes"
-- ACTION 13: pressed "BACK" button to navigate back</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Sort by"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1425,19 +1369,10 @@
 - ACTION 4: touched on a button that has text "Yes"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has text "Manage shown tabs"
-- ACTION 4: pressed "BACK" button to navigate back
-- ACTION 5: touched on a button that has text "Manage shown tabs"
-- ACTION 6: touched on a checked checkbox that has text "Groups"
-- ACTION 7: touched on a checked checkbox that has text "Favorites"
-- ACTION 8: touched on a button that has text "OK"
-- ACTION 9: touched on a button that has text "Manage shown tabs"
-- ACTION 10: touched on a checkbox that has text "Favorites"
-- ACTION 11: touched on a button that has text "OK"
-- ACTION 12: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
-- ACTION 13: touched on a checkbox that has text "Show a dialpad button on the main screen"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 3: Jade Green touched on a checked checkbox that has text "Show a dialpad button on the main screen"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -1451,24 +1386,14 @@
 - ACTION 2: touched on a button that has content-desc "Call contact"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Dialpad"
-- ACTION 3: Open the app again because the previous action led to closing the app
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has text "Dialpad"
-- ACTION 6: Open the app again because the previous action led to closing the app
-- ACTION 7: touched on a button that has content-desc "More options"
-- ACTION 8: touched on a button that has text "Dialpad"
-- ACTION 9: Open the app again because the previous action led to closing the app
-- ACTION 10: touched on a button that has content-desc "Create new contact"
-- ACTION 11: pressed "BACK" button to navigate back
-- ACTION 12: touched on a button that has content-desc "More options"
-- ACTION 13: touched on a button that has text "Dialpad"
-- ACTION 14: Open the app again because the previous action led to closing the app
-- ACTION 15: touched on a button that has content-desc "More options"
-- ACTION 16: touched on a button that has text "Dialpad"
-- ACTION 17: Open the app again because the previous action led to closing the app
-- ACTION 18: touched on a button that has content-desc "Sort by"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Call number"
+- ACTION 2: Jade Green touched on a button that has content_desc "Dialpad"
+- ACTION 3: Jade Green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- ACTION 4: Jade Green touched on a button that has content_desc "Call number"
+- ACTION 5: Jade Green touched on a button that has content_desc "Dialpad"
+- ACTION 6: Jade Green touched on a button that has content_desc "Call number"
+- ACTION 7: Jade Green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Bob"
@@ -1477,9 +1402,10 @@
 - ACTION 4: touched on a button that has text "SMS"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has text "Manage shown contact fields"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Manage shown contact fields"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Sort by"
@@ -1499,30 +1425,11 @@
 - ACTION 4: touched on a button that has text "Medium"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Dialpad"
-- ACTION 2: filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
-- ACTION 3: touched on a button that has content-desc "Call number"
-- ACTION 4: Open the app again because the previous action led to closing the app
-- ACTION 5: touched on a button that has content-desc "Call number"
-- ACTION 6: Open the app again because the previous action led to closing the app
-- ACTION 7: touched on a button that has content-desc "Call number"
-- ACTION 8: Open the app again because the previous action led to closing the app
-- ACTION 9: touched on a button that has content-desc "Call number"
-- ACTION 10: Open the app again because the previous action led to closing the app
-- ACTION 11: touched on a button that has content-desc "Call number"
-- ACTION 12: Open the app again because the previous action led to closing the app
-- ACTION 13: touched on a button that has content-desc "Call number"
-- ACTION 14: Open the app again because the previous action led to closing the app
-- ACTION 15: touched on a button that has content-desc "Call number"
-- ACTION 16: Open the app again because the previous action led to closing the app
-- ACTION 17: touched on a button that has content-desc "Call number"
-- ACTION 18: Open the app again because the previous action led to closing the app
-- ACTION 19: touched on a button that has content-desc "Call number"
-- ACTION 20: Open the app again because the previous action led to closing the app
-- ACTION 21: touched on a button that has content-desc "Call number"
-- ACTION 22: Open the app again because the previous action led to closing the app
-- ACTION 23: touched on a button that has content-desc "Call number"
-- ACTION 24: Open the app again because the previous action led to closing the app</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Back"
+- ACTION 2: Jade Green touched on a button that has content_desc "Dialpad"
+- ACTION 3: Jade Green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- ACTION 4: Jade Green touched on a button that has content_desc "Call number"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Alice"
@@ -1536,35 +1443,6 @@
 - ACTION 2: filled a textfield that has text "First name" with the text "Alice"
 - ACTION 3: filled a textfield that has text "Number" with the text "31232134"
 - ACTION 4: touched on a button that has content-desc "Save"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Back"
-- ACTION 2: Open the app again because you stayed on the pages not belonging to the target app for too long
-- ACTION 3: touched on a button that has text "Phone"
-- ACTION 4: touched on a button that has text "Call History"
-- ACTION 5: touched on a button that has text "Call History"
-- ACTION 6: touched on a button that has text "Call History"
-- ACTION 7: touched on a button that has text "Call History"
-- ACTION 8: touched on a button that has text "Call History"
-- ACTION 9: touched on a button that has text "Call History"
-- ACTION 10: touched on a button that has text "Call History"
-- ACTION 11: touched on a button that has text "Call History"
-- ACTION 12: touched on a button that has text "Call History"
-- ACTION 13: touched on a button that has text "Call History"
-- ACTION 14: touched on a button that has text "Call History"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: long touched on a button that has text "Jack"
-- ACTION 2: touched on a button that has content-desc "Delete"
-- ACTION 3: touched on a button that has text "Yes"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a checkbox that has text "Hide dialpad numbers"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Favorites"</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Create new contact"
@@ -1575,14 +1453,25 @@
 - ACTION 6: touched on a button that has content-desc "Save"</t>
   </si>
   <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Call History"
+- ACTION 2: Jade Green touched on a button that has content_desc "Clear call history"
+- ACTION 3: Jade Green touched on a button that has text "Yes"
+</t>
+  </si>
+  <si>
+    <t>- ACTION 1: long touched on a button that has text "Jack"
+- ACTION 2: touched on a button that has content-desc "Delete"
+- ACTION 3: touched on a button that has text "Yes"</t>
+  </si>
+  <si>
+    <t>- ACTION 1: scrolled down on a scrollable area that has text "Alice, Alice, Bob[...and more]"
+- ACTION 2: touched on a button that has text "Alice"</t>
+  </si>
+  <si>
     <t>- ACTION 1: touched on a button that has text "Alice"
 - ACTION 2: touched on a button that has content-desc "Edit contact"
 - ACTION 3: filled a textfield that has text "11111111" with the text "1234567890"
 - ACTION 4: touched on a button that has content-desc "Save"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: scrolled down on a scrollable area that has text "Alice, Alice, Bob[...and more]"
-- ACTION 2: touched on a button that has text "Alice"</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Sort by"
@@ -1597,6 +1486,14 @@
 - ACTION 5: touched on a button that has text "SMS"</t>
   </si>
   <si>
+    <t>- ACTION 1: touched on a button that has content-desc "More options"
+- ACTION 2: touched on a button that has text "Settings"
+- ACTION 3: touched on a checkbox that has text "Hide dialpad numbers"</t>
+  </si>
+  <si>
+    <t>- ACTION 1: touched on a button that has text "Favorites"</t>
+  </si>
+  <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
 - ACTION 2: touched on a button that has text "Manage favorites"
 - ACTION 3: touched on a button that has content-desc "Add favorites"
@@ -1614,19 +1511,12 @@
 </t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
-- ACTION 3: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 4: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 5: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 6: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 7: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 8: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 9: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 10: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 11: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 12: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
-- ACTION 13: scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "Require pressing Back twice to leave the app, VISIBILITY, Show hidden items[...and more]"
+- ACTION 4: Jade Green pressed "BACK" button to navigate back
+- ACTION 5: Jade Green touched on a button that has text "SD Card, 835.5 MB, free[...and more]"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1658,13 +1548,16 @@
 - ACTION 2: touched on a button that has text "video2.mp4, 64.7 kB, 12.08.2024, 06:00 PM"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Apps list"
-- ACTION 2: touched on a button that has text "Recents"
-- ACTION 3: scrolled down on a scrollable area that has text "Screenshot_20240910-202318.png, 245.8 kB, 10.09.2024, 08:23 PM[...and more]"
-- ACTION 4: scrolled down on a scrollable area that has text "test.ics, 2 kB, 10.09.2024, 07:09 PM[...and more]"
-- ACTION 5: scrolled down on a scrollable area that has text "test.ics, 2 kB, 10.09.2024, 07:09 PM[...and more]"
-- ACTION 6: touched on a button that has content-desc "Search"
-- ACTION 7: filled a focused textfield that has text "Search" with the text "test1.m4a"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green scrolled right on a scrollable area that has text "Internal, 4.7 GB, free[...and more]"
+- ACTION 2: Jade Green touched on a button that has text "Files"
+- ACTION 3: Jade Green scrolled right on a scrollable area that has text "Internal, Download, 22 items[...and more]"
+- ACTION 4: Jade Green scrolled right on a scrollable area that has text "Internal, 4.7 GB, free[...and more]"
+- ACTION 5: Jade Green touched on a button that has text "Files"
+- ACTION 6: Jade Green scrolled down on a scrollable area that has text "Download, 22 items, DCIM[...and more]"
+- ACTION 7: Jade Green scrolled down on a scrollable area that has text "Alarms_New, 0 items, Notifications[...and more]"
+- ACTION 8: Jade Green touched on a button that has content_desc "Search"
+- ACTION 9: Jade Green filled a focused textfield that has text "Search" with the text "test1.m4a"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Android, 3 items"
@@ -1693,8 +1586,10 @@
 - ACTION 4: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a checkbox that has text "Show hidden items"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green touched on a checked checkbox that has text "Show hidden items"
+- ACTION 3: Jade Green touched on a checkbox that has text "Show hidden items"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -1715,16 +1610,18 @@
 - ACTION 3: touched on a button that has text "5 columns"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
-- ACTION 4: scrolled down on a scrollable area that has text "Always open videos on a separate screen with new h[...], Allow controlling video volume and brightness with[...], THUMBNAILS[...and more]"
-- ACTION 5: scrolled down on a scrollable area that has text "Allow instantly changing media by clicking on scre[...], Allow controlling photo brightness with vertical g[...], Allow closing the fullscreen view with a down gest[...][...and more]"
-- ACTION 6: scrolled down on a scrollable area that has text "Password protect the whole application, Password protect hidden item visibility, Password protect file deletion and moving[...and more]"
-- ACTION 7: scrolled down on a scrollable area that has text "RECYCLE BIN, Move items into the Recycle Bin instead of deletin[...], Show the Recycle Bin at the folders screen[...and more]"
-- ACTION 8: scrolled down on a scrollable area that has text "RECYCLE BIN, Move items into the Recycle Bin instead of deletin[...], Show the Recycle Bin at the folders screen[...and more]"
-- ACTION 9: touched on a checked checkbox that has text "GIFs"
-- ACTION 10: touched on a button that has text "OK"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "Always open videos on a separate screen with new h[...], Allow controlling video volume and brightness with[...], THUMBNAILS[...and more]"
+- ACTION 5: Jade Green scrolled down on a scrollable area that has text "Allow instantly changing media by clicking on scre[...], Allow controlling photo brightness with vertical g[...], Allow closing the fullscreen view with a down gest[...][...and more]"
+- ACTION 6: Jade Green scrolled down on a scrollable area that has text "Password protect hidden item visibility, Password protect file deletion and moving, FILE OPERATIONS[...and more]"
+- ACTION 7: Jade Green scrolled up on a scrollable area that has text "RECYCLE BIN, Move items into the Recycle Bin instead of deletin[...], Show the Recycle Bin at the folders screen[...and more]"
+- ACTION 8: Jade Green scrolled up on a scrollable area that has text "Allow 1:1 zooming in with two double taps, EXTENDED DETAILS, Show extended details over fullscreen media[...and more]"
+- ACTION 9: Jade Green scrolled up on a scrollable area that has text "FULLSCREEN MEDIA, Max brightness when viewing fullscreen media, Black background at fullscreen media[...and more]"
+- ACTION 10: Jade Green touched on a button that has text "File thumbnail style"
+- ACTION 11: Jade Green touched on a checkbox that has text "Animate GIFs at thumbnails"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "DCIM, 3, /storage/emulated/0/"
@@ -1761,19 +1658,14 @@
 - ACTION 3: Open the app again because the previous action led to closing the app</t>
   </si>
   <si>
-    <t>- ACTION 1: long touched on a button that has text "Alice, I love you, 09.09"
-- ACTION 2: touched on a button that has content-desc "More options"
-- ACTION 3: pressed "BACK" button to navigate back
-- ACTION 4: long touched on a selected button that has text "Alice, I love you, 09.09"
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: pressed "BACK" button to navigate back
-- ACTION 7: touched on a button that has content-desc "More options"
-- ACTION 8: touched on a button that has text "Archive"
-- ACTION 9: touched on a button that has text "No"
-- ACTION 10: long touched on a button that has content-desc "More options"
-- ACTION 11: touched on a button that has content-desc "More options"
-- ACTION 12: pressed "BACK" button to navigate back
-- ACTION 13: touched on a button that has content-desc "More options"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green pressed "BACK" button to navigate back
+- ACTION 2: Jade Green touched on a button that has text "Alice, Hi Alice, I wanted to share some exciting news wit[...], 05:14 PM"
+- ACTION 3: Jade Green touched on a button that has content_desc "More options"
+- ACTION 4: Jade Green touched on a button that has text "Conversation details"
+- ACTION 5: Jade Green touched on a button that has text "Alice"
+- ACTION 6: Jade Green filled a focused textfield that has text "Conversation name" with the text "team_discussion"
+- ACTION 7: Jade Green touched on a button that has text "OK"
+</t>
   </si>
   <si>
     <t>- ACTION 1: long touched on a button that has text "Bob, Hi, 10:29 PM"
@@ -1803,19 +1695,11 @@
 - ACTION 3: touched on a button that has text "Mark as Unread"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
-- ACTION 3: scrolled down on a scrollable area that has text "Send message on pressing Enter, Enable delivery reports, Send long messages as MMS[...and more]"
-- ACTION 4: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 5: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 6: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 7: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 8: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 9: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 10: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 11: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 12: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
-- ACTION 13: scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "Send message on pressing Enter, Enable delivery reports, Send long messages as MMS[...and more]"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Alice, I love you, 09.09"
@@ -1823,19 +1707,18 @@
 - ACTION 3: touched on a button that has text "SMS"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has resource_id "com.simplemobiletools.smsmessenger:id/conversations_fab"
-- ACTION 2: filled a focused textfield that has text "Add Contact or Numberâ€¦" with the text "1234567890"
-- ACTION 3: touched on a button that has resource_id "com.simplemobiletools.smsmessenger:id/new_conversation_confirm"
-- ACTION 4: filled a textfield that has text "Type a messageâ€¦" with the text "Hi there! This is a test message to check how the MMS functionality works in the SMS Messenger app. I hope this long message is sent successfully as an MMS. Have a great day!"
-- ACTION 5: touched on a button that has text "SMS"
-- ACTION 6: touched on a button that has content-desc "Attachment"
-- ACTION 7: touched on a button that has text "Choose photo"
-- ACTION 8: pressed "BACK" button to navigate back
-- ACTION 9: touched on a button that has text "Choose photo"
-- ACTION 10: pressed "BACK" button to navigate back
-- ACTION 11: touched on a button that has text "Choose photo"
-- ACTION 12: touched on a button that has text "Large files"
-- ACTION 13: touched on a button that has content-desc "List view"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Start a conversation"
+- ACTION 2: Jade Green touched on a button that has text "Alice, 1234567890"
+- ACTION 3: Jade Green touched on a button that has content_desc "Attachment"
+- ACTION 4: Jade Green touched on a button that has text "Choose photo"
+- ACTION 5: Jade Green touched on a button that has content_desc "Show roots"
+- ACTION 6: Jade Green touched on a button that has text "Images"
+- ACTION 7: Jade Green pressed "BACK" button to navigate back
+- ACTION 8: Jade Green filled a textfield that has text "Hi Alice, I wanted to share some exciting news wit[...]" with the text "Hi Alice, I wanted to share some exciting news with you! I've been working on a new project that combines my passion for technology and sustainability. It's been an incredible journey so far, and I can't wait to tell you all about it. Let's catch up soon over coffee or a call!"
+- ACTION 9: Jade Green touched on a button that has text "SMS"
+- ACTION 10: Jade Green touched on a button that has content_desc "Attachment"
+- ACTION 11: Jade Green touched on a button that has text "Choose photo"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1857,37 +1740,18 @@
     <t>- ACTION 1: touched on a button that has text "Bob, Hi, 10:29 PM"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has text "Manage shown tabs"
-- ACTION 4: pressed "BACK" button to navigate back
-- ACTION 5: touched on a button that has text "Gapless playback"
-- ACTION 6: touched on a button that has text "Customize colors"
-- ACTION 7: pressed "BACK" button to navigate back
-- ACTION 8: touched on a button that has text "Manage excluded folders"
-- ACTION 9: touched on a button that has content-desc "Back"
-- ACTION 10: touched on a button that has text "Manage shown tabs"
-- ACTION 11: touched on a checkbox that has text "Genres"
-- ACTION 12: pressed "BACK" button to navigate back
-- ACTION 13: touched on a button that has content-desc "Back"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Equalizer"
+- ACTION 2: Jade Green touched on a button that has text "Hip Hop"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Recordings, 3 Tracks"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has text "Test1, &lt;unknown&gt; â€¢ Recordings, 00:03"
-- ACTION 2: touched on a button that has content-desc "Play / Pause"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: pressed "BACK" button to navigate back
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: pressed "BACK" button to navigate back
-- ACTION 7: touched on a button that has content-desc "More options"
-- ACTION 8: pressed "BACK" button to navigate back
-- ACTION 9: touched on a button that has content-desc "More options"
-- ACTION 10: pressed "BACK" button to navigate back
-- ACTION 11: touched on a button that has content-desc "Back"
-- ACTION 12: touched on a button that has content-desc "Repeat all"
-- ACTION 13: touched on a button that has content-desc "Repeat current song"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Folders"
+- ACTION 2: Jade Green touched on a button that has text "Recordings, 8 Tracks"
+- ACTION 3: Jade Green touched on a button that has text "test1, &lt;unknown&gt; • Recordings, 00:01"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Tracks"
@@ -1945,15 +1809,18 @@
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Create a new note"
-- ACTION 2: filled a focused textfield that has text "Label" with the text "test"
-- ACTION 3: touched on a button that has text "OK"
-- ACTION 4: filled a focused textfield that has text "test" with the text "12345678"
-- ACTION 5: pressed "BACK" button to navigate back
-- ACTION 6: touched on a focused textfield that has text "12345678"
-- ACTION 7: pressed "BACK" button to navigate back
-- ACTION 8: pressed "BACK" button to navigate back
-- ACTION 9: touched on a button that has content-desc "Search"
-- ACTION 10: filled a focused textfield that has text "Search" with the text "234"</t>
+- ACTION 2: touched on a button that has text "Text note"
+- ACTION 3: filled a focused textfield that has text "Label" with the text "test"
+- ACTION 4: touched on a button that has text "OK"
+- ACTION 5: filled a focused textfield that has text "Insert text here" with the text "123456"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Create a new note"
+- ACTION 2: Jade Green filled a focused textfield that has text "Label" with the text "test"
+- ACTION 3: Jade Green touched on a button that has text "OK"
+- ACTION 4: Jade Green filled a focused textfield that has text "Insert text here" with the text "12345678"
+- ACTION 5: Jade Green touched on a button that has content_desc "Search"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Create a new note"
@@ -1970,16 +1837,14 @@
 - ACTION 7: touched on a button that has text "Delete"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Open note"
-- ACTION 2: touched on a button that has text "Diary"
-- ACTION 3: touched on a button that has text "General note"
-- ACTION 4: touched on a button that has text "Diary"
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: touched on a button that has text "Export as file"
-- ACTION 7: filled a textfield that has text "Diary.txt" with the text "diary.txt"
-- ACTION 8: touched on a button that has text "SAVE"
-- ACTION 9: touched on a button that has text "Only export the current file content
-(changing the[...]"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Search"
+- ACTION 2: Jade Green filled a focused textfield that has text "Search" with the text "Diary"
+- ACTION 3: Jade Green touched on a button that has content_desc "More options"
+- ACTION 4: Jade Green touched on a button that has text "Export as file"
+- ACTION 5: Jade Green filled a textfield that has text "General note.txt" with the text "diary.txt"
+- ACTION 6: Jade Green touched on a button that has text "SAVE"
+- ACTION 7: Jade Green touched on a button that has text "Only export the current file content
+</t>
   </si>
   <si>
     <t xml:space="preserve">- ACTION 1: touched on a button that has text "General note"
@@ -1994,13 +1859,6 @@
 - ACTION 3: touched on a button that has content-desc "Save"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Create a new note"
-- ACTION 2: touched on a button that has text "Text note"
-- ACTION 3: filled a focused textfield that has text "Label" with the text "test"
-- ACTION 4: touched on a button that has text "OK"
-- ACTION 5: filled a focused textfield that has text "Insert text here" with the text "123456"</t>
-  </si>
-  <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
 - ACTION 2: touched on a button that has text "Settings"
 - ACTION 3: scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
@@ -2024,11 +1882,8 @@
 - ACTION 3: touched on a button that has content-desc "Play / Pause"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Search"
-- ACTION 2: filled a focused textfield that has text "Search" with the text "test1"
-- ACTION 3: touched on a button that has text "test1.m4a, 00:05, 12.08.2024, 06:00 PM[...and more]"
-- ACTION 4: touched on a button that has text "test1.m4a, 00:05, 12.08.2024, 06:00 PM[...and more]"
-- ACTION 5: touched on a button that has content-desc "Play / Pause"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green filled a textfield that has text "Search" with the text "test1"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -2066,15 +1921,6 @@
 - ACTION 3: touched on a button that has text "mp3"</t>
   </si>
   <si>
-    <t>VALID</t>
-  </si>
-  <si>
-    <t>OPTIMAL</t>
-  </si>
-  <si>
-    <t>NOTE</t>
-  </si>
-  <si>
     <t>loop</t>
   </si>
   <si>
@@ -2162,8 +2008,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2226,21 +2072,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2278,7 +2116,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2312,7 +2150,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2347,10 +2184,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2523,14 +2359,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I152"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="23.08984375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2550,33 +2383,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>467</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>468</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2585,24 +2418,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2611,24 +2444,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -2637,24 +2470,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2663,24 +2496,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2689,24 +2522,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -2718,24 +2551,24 @@
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2744,24 +2577,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2773,24 +2606,24 @@
         <v>471</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2799,24 +2632,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E11">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2828,24 +2661,24 @@
         <v>472</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" t="s">
-        <v>318</v>
-      </c>
-      <c r="E12">
-        <v>13</v>
-      </c>
       <c r="F12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2857,24 +2690,24 @@
         <v>473</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E13">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2883,24 +2716,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2909,24 +2742,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2935,24 +2768,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D16" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2961,24 +2794,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2987,24 +2820,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E18">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3013,24 +2846,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3039,24 +2872,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -3065,24 +2898,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3091,24 +2924,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D22" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3117,24 +2950,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D23" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3143,24 +2976,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3172,50 +3005,50 @@
         <v>474</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>345</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" t="s">
+        <v>320</v>
+      </c>
+      <c r="E26">
         <v>4</v>
       </c>
-      <c r="F25" t="s">
-        <v>351</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" t="s">
-        <v>317</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
       <c r="F26" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3224,24 +3057,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3250,24 +3083,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3276,24 +3109,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3305,24 +3138,24 @@
         <v>475</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D30" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3334,24 +3167,24 @@
         <v>476</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3360,77 +3193,77 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" t="s">
+        <v>321</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>352</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>200</v>
       </c>
-      <c r="D32" t="s">
-        <v>318</v>
-      </c>
-      <c r="E32">
+      <c r="D33" t="s">
+        <v>321</v>
+      </c>
+      <c r="E33">
         <v>14</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>353</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
         <v>53</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>201</v>
       </c>
-      <c r="D33" t="s">
-        <v>318</v>
-      </c>
-      <c r="E33">
-        <v>13</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="D34" t="s">
+        <v>320</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
         <v>354</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" t="s">
-        <v>318</v>
-      </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>346</v>
-      </c>
       <c r="G34">
         <v>1</v>
       </c>
@@ -3438,9 +3271,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -3449,10 +3282,10 @@
         <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
         <v>355</v>
@@ -3464,24 +3297,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -3490,24 +3323,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -3519,24 +3352,24 @@
         <v>477</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -3545,24 +3378,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D39" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3571,24 +3404,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -3597,24 +3430,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -3626,24 +3459,24 @@
         <v>478</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3652,24 +3485,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D43" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -3681,24 +3514,24 @@
         <v>479</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D44" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -3707,24 +3540,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D45" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -3733,24 +3566,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D46" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -3759,24 +3592,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D47" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3785,24 +3618,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D48" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -3811,24 +3644,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E49">
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3837,24 +3670,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E50">
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -3866,24 +3699,24 @@
         <v>480</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D51" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E51">
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -3892,24 +3725,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D52" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E52">
         <v>5</v>
       </c>
       <c r="F52" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -3921,24 +3754,24 @@
         <v>481</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3947,24 +3780,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E54">
         <v>4</v>
       </c>
       <c r="F54" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -3973,24 +3806,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E55">
         <v>5</v>
       </c>
       <c r="F55" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3999,24 +3832,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E56">
         <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -4025,24 +3858,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E57">
         <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -4051,50 +3884,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58" t="s">
+        <v>378</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
         <v>13</v>
       </c>
-      <c r="F58" t="s">
-        <v>375</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>10</v>
-      </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E59">
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -4103,24 +3936,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D60" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E60">
         <v>2</v>
       </c>
       <c r="F60" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -4129,24 +3962,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E61">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -4155,24 +3988,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D62" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E62">
         <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -4184,24 +4017,24 @@
         <v>482</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C63" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E63">
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -4213,24 +4046,24 @@
         <v>483</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E64">
         <v>4</v>
       </c>
       <c r="F64" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -4239,24 +4072,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D65" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E65">
         <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -4268,24 +4101,24 @@
         <v>484</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D66" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E66">
         <v>4</v>
       </c>
       <c r="F66" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -4294,24 +4127,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D67" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E67">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -4323,24 +4156,24 @@
         <v>485</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D68" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E68">
         <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -4352,24 +4185,24 @@
         <v>486</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D69" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E69">
         <v>4</v>
       </c>
       <c r="F69" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -4378,50 +4211,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D70" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E70">
         <v>6</v>
       </c>
       <c r="F70" t="s">
+        <v>390</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" t="s">
+        <v>320</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71" t="s">
         <v>391</v>
-      </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" t="s">
-        <v>234</v>
-      </c>
-      <c r="D71" t="s">
-        <v>318</v>
-      </c>
-      <c r="E71">
-        <v>14</v>
-      </c>
-      <c r="F71" t="s">
-        <v>387</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -4433,24 +4266,24 @@
         <v>487</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D72" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -4459,24 +4292,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C73" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D73" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -4488,24 +4321,24 @@
         <v>488</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D74" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -4517,24 +4350,24 @@
         <v>489</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D75" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E75">
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -4543,24 +4376,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D76" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E76">
         <v>7</v>
       </c>
       <c r="F76" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -4569,24 +4402,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C77" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D77" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E77">
         <v>5</v>
       </c>
       <c r="F77" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -4598,24 +4431,24 @@
         <v>490</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D78" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -4624,24 +4457,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D79" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -4650,24 +4483,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D80" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E80">
         <v>5</v>
       </c>
       <c r="F80" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4676,24 +4509,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D81" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -4702,24 +4535,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D82" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E82">
         <v>2</v>
       </c>
       <c r="F82" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4728,24 +4561,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C83" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D83" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E83">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -4754,24 +4587,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C84" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D84" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E84">
         <v>6</v>
       </c>
       <c r="F84" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -4780,24 +4613,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C85" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D85" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E85">
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -4806,24 +4639,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C86" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D86" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -4832,24 +4665,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D87" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E87">
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -4858,24 +4691,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C88" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D88" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E88">
         <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -4887,24 +4720,24 @@
         <v>491</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C89" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D89" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E89">
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -4916,24 +4749,24 @@
         <v>492</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C90" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D90" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E90">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -4942,24 +4775,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C91" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D91" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E91">
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -4968,24 +4801,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C92" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E92">
         <v>6</v>
       </c>
       <c r="F92" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -4994,24 +4827,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C93" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D93" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E93">
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -5020,24 +4853,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C94" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D94" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E94">
         <v>4</v>
       </c>
       <c r="F94" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -5046,24 +4879,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D95" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -5072,24 +4905,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C96" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D96" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E96">
         <v>4</v>
       </c>
       <c r="F96" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -5098,24 +4931,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E97">
         <v>5</v>
       </c>
       <c r="F97" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -5124,24 +4957,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C98" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D98" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -5150,24 +4983,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C99" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D99" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F99" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -5176,24 +5009,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D100" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E100">
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -5202,24 +5035,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D101" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -5228,24 +5061,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D102" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E102">
         <v>4</v>
       </c>
       <c r="F102" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -5254,24 +5087,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C103" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D103" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -5280,24 +5113,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C104" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D104" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E104">
         <v>4</v>
       </c>
       <c r="F104" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -5306,24 +5139,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C105" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D105" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -5335,24 +5168,24 @@
         <v>492</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D106" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -5364,24 +5197,24 @@
         <v>493</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C107" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D107" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E107">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -5390,24 +5223,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C108" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D108" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E108">
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -5416,24 +5249,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C109" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D109" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E109">
         <v>4</v>
       </c>
       <c r="F109" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -5445,24 +5278,24 @@
         <v>494</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C110" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D110" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E110">
         <v>6</v>
       </c>
       <c r="F110" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -5474,24 +5307,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C111" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D111" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -5503,24 +5336,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C112" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D112" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -5532,24 +5365,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C113" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D113" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E113">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F113" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -5558,24 +5391,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C114" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D114" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -5587,24 +5420,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C115" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D115" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E115">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F115" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -5613,24 +5446,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C116" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D116" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -5639,24 +5472,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D117" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E117">
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -5665,24 +5498,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C118" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D118" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E118">
         <v>5</v>
       </c>
       <c r="F118" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -5691,24 +5524,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C119" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D119" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E119">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -5720,24 +5553,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B120" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C120" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D120" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E120">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -5746,24 +5579,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B121" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C121" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D121" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E121">
         <v>7</v>
       </c>
       <c r="F121" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -5772,24 +5605,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B122" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C122" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D122" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E122">
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -5798,24 +5631,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B123" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C123" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D123" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E123">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -5824,24 +5657,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C124" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D124" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E124">
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5850,24 +5683,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C125" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D125" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -5876,24 +5709,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B126" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C126" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D126" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -5902,24 +5735,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C127" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D127" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E127">
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -5928,24 +5761,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B128" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C128" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D128" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
       <c r="F128" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -5954,24 +5787,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B129" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C129" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D129" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E129">
         <v>4</v>
       </c>
       <c r="F129" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -5980,24 +5813,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B130" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C130" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D130" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E130">
         <v>8</v>
       </c>
       <c r="F130" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -6006,24 +5839,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C131" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D131" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E131">
         <v>4</v>
       </c>
       <c r="F131" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -6032,24 +5865,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C132" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D132" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E132">
         <v>4</v>
       </c>
       <c r="F132" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -6058,24 +5891,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B133" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D133" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E133">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -6084,24 +5917,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B134" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C134" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D134" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E134">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F134" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -6110,24 +5943,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C135" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D135" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E135">
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -6136,24 +5969,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B136" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D136" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E136">
         <v>7</v>
       </c>
       <c r="F136" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -6162,9 +5995,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B137" t="s">
         <v>153</v>
@@ -6173,10 +6006,10 @@
         <v>304</v>
       </c>
       <c r="D137" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F137" t="s">
         <v>455</v>
@@ -6188,24 +6021,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B138" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C138" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D138" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E138">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -6217,24 +6050,24 @@
         <v>496</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B139" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C139" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D139" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -6246,24 +6079,24 @@
         <v>497</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B140" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C140" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D140" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -6272,24 +6105,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B141" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C141" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D141" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E141">
         <v>5</v>
       </c>
       <c r="F141" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -6298,24 +6131,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B142" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C142" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D142" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E142">
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -6324,24 +6157,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C143" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D143" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F143" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -6353,24 +6186,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B144" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D144" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -6382,24 +6215,24 @@
         <v>495</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B145" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C145" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D145" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>359</v>
+        <v>463</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -6408,24 +6241,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B146" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C146" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D146" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -6437,102 +6270,102 @@
         <v>495</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C147" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D147" t="s">
+        <v>320</v>
+      </c>
+      <c r="E147">
+        <v>6</v>
+      </c>
+      <c r="F147" t="s">
+        <v>465</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>20</v>
+      </c>
+      <c r="B148" t="s">
+        <v>164</v>
+      </c>
+      <c r="C148" t="s">
+        <v>315</v>
+      </c>
+      <c r="D148" t="s">
+        <v>320</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148" t="s">
+        <v>466</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>20</v>
+      </c>
+      <c r="B149" t="s">
+        <v>165</v>
+      </c>
+      <c r="C149" t="s">
+        <v>316</v>
+      </c>
+      <c r="D149" t="s">
+        <v>320</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>362</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>20</v>
+      </c>
+      <c r="B150" t="s">
+        <v>166</v>
+      </c>
+      <c r="C150" t="s">
         <v>317</v>
       </c>
-      <c r="E147">
-        <v>5</v>
-      </c>
-      <c r="F147" t="s">
-        <v>459</v>
-      </c>
-      <c r="G147">
-        <v>1</v>
-      </c>
-      <c r="H147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>17</v>
-      </c>
-      <c r="B148" t="s">
-        <v>163</v>
-      </c>
-      <c r="C148" t="s">
-        <v>314</v>
-      </c>
-      <c r="D148" t="s">
-        <v>317</v>
-      </c>
-      <c r="E148">
-        <v>3</v>
-      </c>
-      <c r="F148" t="s">
-        <v>464</v>
-      </c>
-      <c r="G148">
-        <v>1</v>
-      </c>
-      <c r="H148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>17</v>
-      </c>
-      <c r="B149" t="s">
-        <v>164</v>
-      </c>
-      <c r="C149" t="s">
-        <v>315</v>
-      </c>
-      <c r="D149" t="s">
-        <v>317</v>
-      </c>
-      <c r="E149">
-        <v>3</v>
-      </c>
-      <c r="F149" t="s">
-        <v>465</v>
-      </c>
-      <c r="G149">
-        <v>1</v>
-      </c>
-      <c r="H149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>17</v>
-      </c>
-      <c r="B150" t="s">
-        <v>165</v>
-      </c>
-      <c r="C150" t="s">
-        <v>316</v>
-      </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E150">
         <v>3</v>
       </c>
       <c r="F150" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -6541,24 +6374,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C151" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F151" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -6567,24 +6400,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C152" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -6594,7 +6427,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F152" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>